--- a/Libraries/Vehicle/Dampers/Damper/sm_car_data_Damper_AsymmetricLinear.xlsx
+++ b/Libraries/Vehicle/Dampers/Damper/sm_car_data_Damper_AsymmetricLinear.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\veh-tpl\Libraries\Vehicle\Dampers\Damper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Dampers\Damper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A668DD-1899-426A-AD5F-074FF9440929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD3F1F5-B44A-4B20-A2CA-389B072A7AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10905" yWindow="810" windowWidth="19800" windowHeight="13560" tabRatio="967" activeTab="1" xr2:uid="{C5A4D212-38D5-4645-961A-DE2D82DDDABE}"/>
+    <workbookView xWindow="1530" yWindow="1500" windowWidth="21600" windowHeight="11295" tabRatio="967" activeTab="1" xr2:uid="{C5A4D212-38D5-4645-961A-DE2D82DDDABE}"/>
   </bookViews>
   <sheets>
     <sheet name="SUV_Landy_TA2PR_f" sheetId="23" r:id="rId1"/>
-    <sheet name="Sedan_HambaLG_TA2PR_r" sheetId="24" r:id="rId2"/>
+    <sheet name="SUV_Landy_TA2PRNoSteer_r" sheetId="24" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -126,7 +126,7 @@
     <t>sBottomR</t>
   </si>
   <si>
-    <t>Sedan_HambaLG_TA2PR_AsymmetricLinear_A2</t>
+    <t>SUV_Landy_TA2PRNoSteer_AsymmetricLinear_A2</t>
   </si>
 </sst>
 </file>
@@ -1047,7 +1047,7 @@
         <v>0.47799999999999998</v>
       </c>
       <c r="H6" s="17">
-        <v>0.73299999999999998</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="J6" s="13" t="s">
         <v>22</v>
@@ -1075,7 +1075,7 @@
         <v>-0.47799999999999998</v>
       </c>
       <c r="H7" s="17">
-        <v>0.73299999999999998</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="J7" s="13" t="s">
         <v>22</v>
@@ -1128,7 +1128,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="G9" s="17">
-        <v>-0.48699999999999999</v>
+        <v>-0.49299999999999999</v>
       </c>
       <c r="H9" s="17">
         <v>0.52300000000000002</v>
@@ -1157,8 +1157,7 @@
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="18">
-        <f>0.25+H11</f>
-        <v>0.10500000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J10" s="14" t="s">
         <v>22</v>
@@ -1179,7 +1178,7 @@
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="18">
-        <v>-0.14499999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="J11" s="14" t="s">
         <v>22</v>
